--- a/src/test/resources/Data/TestData.xlsx
+++ b/src/test/resources/Data/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fahim\IdeaProjects\Automation_Playwright\src\test\resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA02987-49C0-4549-ADC7-92140FD62FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63569D9-A46E-4E22-8500-85BB1E2CED35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="3720" windowWidth="17280" windowHeight="9960" xr2:uid="{787EAEBE-C150-4F3F-A023-F6B82C3B6518}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>ExecuteTestCase</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>PL_1</t>
+  </si>
+  <si>
+    <t>PL_2</t>
   </si>
 </sst>
 </file>
@@ -441,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC91D37C-980A-4460-8A9B-A18F05568BC5}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="1" customWidth="1"/>
@@ -465,6 +468,14 @@
         <v>3</v>
       </c>
     </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/Data/TestData.xlsx
+++ b/src/test/resources/Data/TestData.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fahim\IdeaProjects\Automation_Playwright\src\test\resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63569D9-A46E-4E22-8500-85BB1E2CED35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8CC2CA4-9C20-408D-B3BB-3C64F40F562B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3720" windowWidth="17280" windowHeight="9960" xr2:uid="{787EAEBE-C150-4F3F-A023-F6B82C3B6518}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{787EAEBE-C150-4F3F-A023-F6B82C3B6518}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
+    <sheet name="Home" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
   <si>
     <t>ExecuteTestCase</t>
   </si>
@@ -54,6 +55,9 @@
   </si>
   <si>
     <t>PL_2</t>
+  </si>
+  <si>
+    <t>PL_3</t>
   </si>
 </sst>
 </file>
@@ -479,4 +483,30 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652AF9A0-4971-4D5B-A203-284B148DCD0B}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>